--- a/artfynd/A 9436-2025 artfynd.xlsx
+++ b/artfynd/A 9436-2025 artfynd.xlsx
@@ -680,11 +680,6 @@
       <c r="B2" t="n">
         <v>5196</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>LC</t>

--- a/artfynd/A 9436-2025 artfynd.xlsx
+++ b/artfynd/A 9436-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123953336</v>
       </c>
       <c r="B2" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
